--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E926"/>
+  <dimension ref="A1:E927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19876,6 +19876,27 @@
         <v>197.41</v>
       </c>
       <c r="E926" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B927" t="n">
+        <v>216.04</v>
+      </c>
+      <c r="C927" t="n">
+        <v>210.48</v>
+      </c>
+      <c r="D927" t="n">
+        <v>197.49</v>
+      </c>
+      <c r="E927" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19892,7 +19913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1058"/>
+  <dimension ref="A1:B1059"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30475,6 +30496,16 @@
       </c>
       <c r="B1058" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -30637,28 +30668,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02766808056219099</v>
+        <v>-0.02743123012195445</v>
       </c>
       <c r="J2" t="n">
+        <v>926</v>
+      </c>
+      <c r="K2" t="n">
         <v>925</v>
       </c>
-      <c r="K2" t="n">
-        <v>924</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.005038526247477138</v>
+        <v>0.004964459612932126</v>
       </c>
       <c r="M2" t="n">
-        <v>2.461938488876927</v>
+        <v>2.460494294693758</v>
       </c>
       <c r="N2" t="n">
-        <v>8.516816084830511</v>
+        <v>8.508892727810066</v>
       </c>
       <c r="O2" t="n">
-        <v>2.918358457220516</v>
+        <v>2.917000638980058</v>
       </c>
       <c r="P2" t="n">
-        <v>215.6766785092236</v>
+        <v>215.6742839514051</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30709,28 +30740,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04900815947607288</v>
+        <v>-0.04874746671494808</v>
       </c>
       <c r="J3" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="K3" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0166270652938908</v>
+        <v>0.0164902151125873</v>
       </c>
       <c r="M3" t="n">
-        <v>2.311252861845807</v>
+        <v>2.310095439127082</v>
       </c>
       <c r="N3" t="n">
-        <v>8.029293635528413</v>
+        <v>8.022185627498304</v>
       </c>
       <c r="O3" t="n">
-        <v>2.833600825015481</v>
+        <v>2.832346311364185</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5680014264793</v>
+        <v>210.5653724538922</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30781,28 +30812,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06971918735333968</v>
+        <v>-0.0705692724246559</v>
       </c>
       <c r="J4" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="K4" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04001685949308831</v>
+        <v>0.04095598093897479</v>
       </c>
       <c r="M4" t="n">
-        <v>2.032257907612815</v>
+        <v>2.034194366198632</v>
       </c>
       <c r="N4" t="n">
-        <v>6.591179552683006</v>
+        <v>6.600680762267573</v>
       </c>
       <c r="O4" t="n">
-        <v>2.567329264563275</v>
+        <v>2.569179005493306</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2580359890097</v>
+        <v>203.2666087255119</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30840,7 +30871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E926"/>
+  <dimension ref="A1:E927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55841,6 +55872,33 @@
         </is>
       </c>
     </row>
+    <row r="927">
+      <c r="A927" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>-41.019445747530604,173.01843267491665</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>-41.018747425587925,173.01847532716286</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>-41.018064393822094,173.01873048161227</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E927"/>
+  <dimension ref="A1:E929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19897,6 +19897,48 @@
         <v>197.49</v>
       </c>
       <c r="E927" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B928" t="n">
+        <v>215.97</v>
+      </c>
+      <c r="C928" t="n">
+        <v>210.17</v>
+      </c>
+      <c r="D928" t="n">
+        <v>198.36</v>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B929" t="n">
+        <v>217.07</v>
+      </c>
+      <c r="C929" t="n">
+        <v>210.32</v>
+      </c>
+      <c r="D929" t="n">
+        <v>197.99</v>
+      </c>
+      <c r="E929" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19913,7 +19955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1059"/>
+  <dimension ref="A1:B1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30506,6 +30548,26 @@
       </c>
       <c r="B1059" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -30668,28 +30730,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02743123012195445</v>
+        <v>-0.02675195835642269</v>
       </c>
       <c r="J2" t="n">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="K2" t="n">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004964459612932126</v>
+        <v>0.004742650376470259</v>
       </c>
       <c r="M2" t="n">
-        <v>2.460494294693758</v>
+        <v>2.458665475037702</v>
       </c>
       <c r="N2" t="n">
-        <v>8.508892727810066</v>
+        <v>8.496483436628836</v>
       </c>
       <c r="O2" t="n">
-        <v>2.917000638980058</v>
+        <v>2.914872799390882</v>
       </c>
       <c r="P2" t="n">
-        <v>215.6742839514051</v>
+        <v>215.6674055685167</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30740,28 +30802,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04874746671494808</v>
+        <v>-0.04832986222008698</v>
       </c>
       <c r="J3" t="n">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="K3" t="n">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0164902151125873</v>
+        <v>0.0162879224652509</v>
       </c>
       <c r="M3" t="n">
-        <v>2.310095439127082</v>
+        <v>2.307250271591393</v>
       </c>
       <c r="N3" t="n">
-        <v>8.022185627498304</v>
+        <v>8.006918862845893</v>
       </c>
       <c r="O3" t="n">
-        <v>2.832346311364185</v>
+        <v>2.829649954119041</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5653724538922</v>
+        <v>210.5611549155806</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30812,28 +30874,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0705692724246559</v>
+        <v>-0.071958469456394</v>
       </c>
       <c r="J4" t="n">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="K4" t="n">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04095598093897479</v>
+        <v>0.04257735163957022</v>
       </c>
       <c r="M4" t="n">
-        <v>2.034194366198632</v>
+        <v>2.036567537301356</v>
       </c>
       <c r="N4" t="n">
-        <v>6.600680762267573</v>
+        <v>6.608773848762011</v>
       </c>
       <c r="O4" t="n">
-        <v>2.569179005493306</v>
+        <v>2.570753556598145</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2666087255119</v>
+        <v>203.280638586214</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30871,7 +30933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E927"/>
+  <dimension ref="A1:E929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55899,6 +55961,60 @@
         </is>
       </c>
     </row>
+    <row r="928">
+      <c r="A928" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>-41.01944572681265,173.01843184279417</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>-41.01874685215053,173.01847171867047</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>-41.01806957862943,173.01873824101799</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>-41.019446052379955,173.01844491900516</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>-41.018747129620245,173.01847346471513</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>-41.01806737359649,173.01873494104066</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E929"/>
+  <dimension ref="A1:E932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19939,6 +19939,69 @@
         <v>197.99</v>
       </c>
       <c r="E929" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>216.88</v>
+      </c>
+      <c r="C930" t="n">
+        <v>209.56</v>
+      </c>
+      <c r="D930" t="n">
+        <v>198.65</v>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:42+00:00</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>216.22</v>
+      </c>
+      <c r="C931" t="n">
+        <v>209.19</v>
+      </c>
+      <c r="D931" t="n">
+        <v>199.47</v>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>215.79</v>
+      </c>
+      <c r="C932" t="n">
+        <v>208.87</v>
+      </c>
+      <c r="D932" t="n">
+        <v>199.92</v>
+      </c>
+      <c r="E932" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19955,7 +20018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1061"/>
+  <dimension ref="A1:B1065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30568,6 +30631,46 @@
       </c>
       <c r="B1061" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -30730,28 +30833,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02675195835642269</v>
+        <v>-0.02588951008969812</v>
       </c>
       <c r="J2" t="n">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="K2" t="n">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004742650376470259</v>
+        <v>0.004472549762812306</v>
       </c>
       <c r="M2" t="n">
-        <v>2.458665475037702</v>
+        <v>2.45516209875564</v>
       </c>
       <c r="N2" t="n">
-        <v>8.496483436628836</v>
+        <v>8.475430509685651</v>
       </c>
       <c r="O2" t="n">
-        <v>2.914872799390882</v>
+        <v>2.911259265281203</v>
       </c>
       <c r="P2" t="n">
-        <v>215.6674055685167</v>
+        <v>215.6586513542932</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30802,28 +30905,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04832986222008698</v>
+        <v>-0.04837746937817222</v>
       </c>
       <c r="J3" t="n">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="K3" t="n">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0162879224652509</v>
+        <v>0.01643768492510767</v>
       </c>
       <c r="M3" t="n">
-        <v>2.307250271591393</v>
+        <v>2.300641524458746</v>
       </c>
       <c r="N3" t="n">
-        <v>8.006918862845893</v>
+        <v>7.981390720362144</v>
       </c>
       <c r="O3" t="n">
-        <v>2.829649954119041</v>
+        <v>2.825135522477133</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5611549155806</v>
+        <v>210.5616392758237</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30874,28 +30977,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.071958469456394</v>
+        <v>-0.0732603452712885</v>
       </c>
       <c r="J4" t="n">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="K4" t="n">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04257735163957022</v>
+        <v>0.04428517090568029</v>
       </c>
       <c r="M4" t="n">
-        <v>2.036567537301356</v>
+        <v>2.036343968780697</v>
       </c>
       <c r="N4" t="n">
-        <v>6.608773848762011</v>
+        <v>6.601444424159247</v>
       </c>
       <c r="O4" t="n">
-        <v>2.570753556598145</v>
+        <v>2.569327621024467</v>
       </c>
       <c r="P4" t="n">
-        <v>203.280638586214</v>
+        <v>203.2938212301011</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30933,7 +31036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E929"/>
+  <dimension ref="A1:E932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56015,6 +56118,87 @@
         </is>
       </c>
     </row>
+    <row r="930">
+      <c r="A930" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:07:29+00:00</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>-41.01944599614571,173.01844266038688</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>-41.01874572377336,173.01846461808884</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>-41.018071306898435,173.0187408274868</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:42+00:00</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>-41.019445800805336,173.01843481466028</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>-41.01874503934764,173.01846031117879</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>-41.018076193727694,173.01874814095115</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>-41.01944567353785,173.01842970305057</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>-41.01874444741176,173.01845658628372</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>-41.018078875524054,173.01875215443815</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E932"/>
+  <dimension ref="A1:E936"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20002,6 +20002,90 @@
         <v>199.92</v>
       </c>
       <c r="E932" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B933" t="n">
+        <v>215.03</v>
+      </c>
+      <c r="C933" t="n">
+        <v>208.23</v>
+      </c>
+      <c r="D933" t="n">
+        <v>200.04</v>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B934" t="n">
+        <v>214.07</v>
+      </c>
+      <c r="C934" t="n">
+        <v>207.32</v>
+      </c>
+      <c r="D934" t="n">
+        <v>200.3</v>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B935" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="C935" t="n">
+        <v>207.02</v>
+      </c>
+      <c r="D935" t="n">
+        <v>200.29</v>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B936" t="n">
+        <v>213.24</v>
+      </c>
+      <c r="C936" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="D936" t="n">
+        <v>200.64</v>
+      </c>
+      <c r="E936" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20018,7 +20102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1065"/>
+  <dimension ref="A1:B1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30671,6 +30755,46 @@
       </c>
       <c r="B1065" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>
@@ -30833,28 +30957,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02588951008969812</v>
+        <v>-0.0267759681151665</v>
       </c>
       <c r="J2" t="n">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="K2" t="n">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004472549762812306</v>
+        <v>0.004825799427757183</v>
       </c>
       <c r="M2" t="n">
-        <v>2.45516209875564</v>
+        <v>2.449066957537238</v>
       </c>
       <c r="N2" t="n">
-        <v>8.475430509685651</v>
+        <v>8.445793833971535</v>
       </c>
       <c r="O2" t="n">
-        <v>2.911259265281203</v>
+        <v>2.906164798144031</v>
       </c>
       <c r="P2" t="n">
-        <v>215.6586513542932</v>
+        <v>215.667691654969</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30905,28 +31029,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04837746937817222</v>
+        <v>-0.04985413665770348</v>
       </c>
       <c r="J3" t="n">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="K3" t="n">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01643768492510767</v>
+        <v>0.01757828881880241</v>
       </c>
       <c r="M3" t="n">
-        <v>2.300641524458746</v>
+        <v>2.297953689446866</v>
       </c>
       <c r="N3" t="n">
-        <v>7.981390720362144</v>
+        <v>7.960763497949444</v>
       </c>
       <c r="O3" t="n">
-        <v>2.825135522477133</v>
+        <v>2.821482500025376</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5616392758237</v>
+        <v>210.5766529449403</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30977,28 +31101,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0732603452712885</v>
+        <v>-0.07413549725880438</v>
       </c>
       <c r="J4" t="n">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="K4" t="n">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04428517090568029</v>
+        <v>0.04569678265244104</v>
       </c>
       <c r="M4" t="n">
-        <v>2.036343968780697</v>
+        <v>2.031861480014128</v>
       </c>
       <c r="N4" t="n">
-        <v>6.601444424159247</v>
+        <v>6.5778526435561</v>
       </c>
       <c r="O4" t="n">
-        <v>2.569327621024467</v>
+        <v>2.564732470172299</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2938212301011</v>
+        <v>203.3027159900713</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31036,7 +31160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E932"/>
+  <dimension ref="A1:E936"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56199,6 +56323,114 @@
         </is>
       </c>
     </row>
+    <row r="933">
+      <c r="A933" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>-41.01944544859939,173.0184206685776</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>-41.01874326353965,173.0184491364937</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>-41.01807959066972,173.0187532247014</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>-41.0194451644656,173.01840925661185</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>-41.01874158022065,173.01843854382403</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>-41.01808114015196,173.0187555436052</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>-41.01944496616321,173.01840129201082</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>-41.018741025280114,173.0184350517352</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>-41.0180810805565,173.0187554544166</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>-41.01944491880734,173.01839939001655</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>-41.018742098165056,173.01844180310692</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>-41.018083166397915,173.01875857601803</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E936"/>
+  <dimension ref="A1:E940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20086,6 +20086,90 @@
         <v>200.64</v>
       </c>
       <c r="E936" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B937" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="C937" t="n">
+        <v>207.31</v>
+      </c>
+      <c r="D937" t="n">
+        <v>200.93</v>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B938" t="n">
+        <v>212.91</v>
+      </c>
+      <c r="C938" t="n">
+        <v>207.65</v>
+      </c>
+      <c r="D938" t="n">
+        <v>201.53</v>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B939" t="n">
+        <v>212.69</v>
+      </c>
+      <c r="C939" t="n">
+        <v>208.09</v>
+      </c>
+      <c r="D939" t="n">
+        <v>201.72</v>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B940" t="n">
+        <v>213.07</v>
+      </c>
+      <c r="C940" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="D940" t="n">
+        <v>202.43</v>
+      </c>
+      <c r="E940" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20102,7 +20186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1069"/>
+  <dimension ref="A1:B1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30795,6 +30879,46 @@
       </c>
       <c r="B1069" t="n">
         <v>1.71</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -30957,28 +31081,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0267759681151665</v>
+        <v>-0.02855513989804048</v>
       </c>
       <c r="J2" t="n">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="K2" t="n">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004825799427757183</v>
+        <v>0.005526416255296485</v>
       </c>
       <c r="M2" t="n">
-        <v>2.449066957537238</v>
+        <v>2.447249871616678</v>
       </c>
       <c r="N2" t="n">
-        <v>8.445793833971535</v>
+        <v>8.428323170299073</v>
       </c>
       <c r="O2" t="n">
-        <v>2.906164798144031</v>
+        <v>2.903157448416994</v>
       </c>
       <c r="P2" t="n">
-        <v>215.667691654969</v>
+        <v>215.6858946474179</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31029,28 +31153,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04985413665770348</v>
+        <v>-0.05091866222014657</v>
       </c>
       <c r="J3" t="n">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="K3" t="n">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01757828881880241</v>
+        <v>0.01848135781682869</v>
       </c>
       <c r="M3" t="n">
-        <v>2.297953689446866</v>
+        <v>2.293290154280333</v>
       </c>
       <c r="N3" t="n">
-        <v>7.960763497949444</v>
+        <v>7.935019007052118</v>
       </c>
       <c r="O3" t="n">
-        <v>2.821482500025376</v>
+        <v>2.816916577936258</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5766529449403</v>
+        <v>210.5875135156744</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31101,28 +31225,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07413549725880438</v>
+        <v>-0.07385706684409149</v>
       </c>
       <c r="J4" t="n">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="K4" t="n">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04569678265244104</v>
+        <v>0.04578449460002931</v>
       </c>
       <c r="M4" t="n">
-        <v>2.031861480014128</v>
+        <v>2.025486762834909</v>
       </c>
       <c r="N4" t="n">
-        <v>6.5778526435561</v>
+        <v>6.5515111012314</v>
       </c>
       <c r="O4" t="n">
-        <v>2.564732470172299</v>
+        <v>2.559591979443482</v>
       </c>
       <c r="P4" t="n">
-        <v>203.3027159900713</v>
+        <v>203.2998708235335</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31160,7 +31284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E936"/>
+  <dimension ref="A1:E940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56431,6 +56555,114 @@
         </is>
       </c>
     </row>
+    <row r="937">
+      <c r="A937" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>-41.01944477969928,173.01839380290838</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>-41.018741561722635,173.01843842742105</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>-41.01808489466646,173.01876116248792</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>-41.01944482113574,173.01839546715337</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>-41.018742190655125,173.01844238512174</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>-41.018088470394275,173.0187665138054</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>-41.01944475602128,173.01839285191124</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>-41.018743004567554,173.01844750685217</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>-41.01808960270803,173.01876820838936</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>-41.01944486849169,173.01839736914764</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>-41.01874450290576,173.0184569354926</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>-41.018093833985546,173.0187745407827</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E940"/>
+  <dimension ref="A1:E945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20170,6 +20170,111 @@
         <v>202.43</v>
       </c>
       <c r="E940" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>213.09</v>
+      </c>
+      <c r="C941" t="n">
+        <v>208.49</v>
+      </c>
+      <c r="D941" t="n">
+        <v>202.48</v>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>213.21</v>
+      </c>
+      <c r="C942" t="n">
+        <v>208.42</v>
+      </c>
+      <c r="D942" t="n">
+        <v>202.23</v>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>212.2</v>
+      </c>
+      <c r="C943" t="n">
+        <v>208</v>
+      </c>
+      <c r="D943" t="n">
+        <v>202.42</v>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>212.23</v>
+      </c>
+      <c r="C944" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="D944" t="n">
+        <v>202.25</v>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>212.89</v>
+      </c>
+      <c r="C945" t="n">
+        <v>207.99</v>
+      </c>
+      <c r="D945" t="n">
+        <v>202.46</v>
+      </c>
+      <c r="E945" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20186,7 +20291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1073"/>
+  <dimension ref="A1:B1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30919,6 +31024,56 @@
       </c>
       <c r="B1073" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -31081,28 +31236,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02855513989804048</v>
+        <v>-0.03086605985139148</v>
       </c>
       <c r="J2" t="n">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="K2" t="n">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005526416255296485</v>
+        <v>0.006509344014972829</v>
       </c>
       <c r="M2" t="n">
-        <v>2.447249871616678</v>
+        <v>2.445383482673115</v>
       </c>
       <c r="N2" t="n">
-        <v>8.428323170299073</v>
+        <v>8.409831110260912</v>
       </c>
       <c r="O2" t="n">
-        <v>2.903157448416994</v>
+        <v>2.899970880933274</v>
       </c>
       <c r="P2" t="n">
-        <v>215.6858946474179</v>
+        <v>215.7096172347597</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31153,28 +31308,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05091866222014657</v>
+        <v>-0.05209674418340435</v>
       </c>
       <c r="J3" t="n">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="K3" t="n">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01848135781682869</v>
+        <v>0.01954404755002748</v>
       </c>
       <c r="M3" t="n">
-        <v>2.293290154280333</v>
+        <v>2.286742008274286</v>
       </c>
       <c r="N3" t="n">
-        <v>7.935019007052118</v>
+        <v>7.900128257574979</v>
       </c>
       <c r="O3" t="n">
-        <v>2.816916577936258</v>
+        <v>2.81071668041711</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5875135156744</v>
+        <v>210.5995789549664</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31225,28 +31380,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07385706684409149</v>
+        <v>-0.07276099835020999</v>
       </c>
       <c r="J4" t="n">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="K4" t="n">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04578449460002931</v>
+        <v>0.04497710583548498</v>
       </c>
       <c r="M4" t="n">
-        <v>2.025486762834909</v>
+        <v>2.020399590108145</v>
       </c>
       <c r="N4" t="n">
-        <v>6.5515111012314</v>
+        <v>6.522573401317656</v>
       </c>
       <c r="O4" t="n">
-        <v>2.559591979443482</v>
+        <v>2.553932928116488</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2998708235335</v>
+        <v>203.2886477601478</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31284,7 +31439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E940"/>
+  <dimension ref="A1:E945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56663,6 +56818,141 @@
         </is>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>-41.019444874411164,173.0183976068969</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>-41.018743744487765,173.01845216297085</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>-41.01809413196281,173.0187749867259</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>-41.01944490992811,173.01839903339263</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>-41.018743615001725,173.01845134815008</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>-41.018092642076425,173.01877275700983</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>-41.01944461099338,173.01838702705382</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>-41.01874283808549,173.0184464592255</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>-41.01809377439009,173.01877445159403</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>-41.01944461987265,173.01838738367778</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>-41.018742098165056,173.01844180310692</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>-41.01809276126733,173.01877293538712</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>-41.019444815216254,173.0183952294041</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>-41.01874281958748,173.0184463428225</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>-41.018094012771904,173.0187748083486</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E945"/>
+  <dimension ref="A1:E949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20277,6 +20277,90 @@
       <c r="E945" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>213.3</v>
+      </c>
+      <c r="C946" t="n">
+        <v>208.75</v>
+      </c>
+      <c r="D946" t="n">
+        <v>202.15</v>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>213.64</v>
+      </c>
+      <c r="C947" t="n">
+        <v>209</v>
+      </c>
+      <c r="D947" t="n">
+        <v>202.01</v>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>213.84</v>
+      </c>
+      <c r="C948" t="n">
+        <v>208.81</v>
+      </c>
+      <c r="D948" t="n">
+        <v>202.18</v>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>214.24</v>
+      </c>
+      <c r="C949" t="n">
+        <v>209.16</v>
+      </c>
+      <c r="D949" t="n">
+        <v>202.1</v>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1078"/>
+  <dimension ref="A1:B1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31074,6 +31158,46 @@
       </c>
       <c r="B1078" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>1.81</v>
       </c>
     </row>
   </sheetData>
@@ -31236,28 +31360,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03086605985139148</v>
+        <v>-0.03180456687789753</v>
       </c>
       <c r="J2" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="K2" t="n">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006509344014972829</v>
+        <v>0.006970302146251273</v>
       </c>
       <c r="M2" t="n">
-        <v>2.445383482673115</v>
+        <v>2.439518876669255</v>
       </c>
       <c r="N2" t="n">
-        <v>8.409831110260912</v>
+        <v>8.380078957563637</v>
       </c>
       <c r="O2" t="n">
-        <v>2.899970880933274</v>
+        <v>2.894836602912786</v>
       </c>
       <c r="P2" t="n">
-        <v>215.7096172347597</v>
+        <v>215.7192804642099</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31308,28 +31432,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05209674418340435</v>
+        <v>-0.05232175853179667</v>
       </c>
       <c r="J3" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="K3" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01954404755002748</v>
+        <v>0.01989624544610125</v>
       </c>
       <c r="M3" t="n">
-        <v>2.286742008274286</v>
+        <v>2.278152104545871</v>
       </c>
       <c r="N3" t="n">
-        <v>7.900128257574979</v>
+        <v>7.867214187611925</v>
       </c>
       <c r="O3" t="n">
-        <v>2.81071668041711</v>
+        <v>2.804855466438855</v>
       </c>
       <c r="P3" t="n">
-        <v>210.5995789549664</v>
+        <v>210.6018898787566</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31380,28 +31504,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07276099835020999</v>
+        <v>-0.07211644860455413</v>
       </c>
       <c r="J4" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="K4" t="n">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04497710583548498</v>
+        <v>0.04461212583225826</v>
       </c>
       <c r="M4" t="n">
-        <v>2.020399590108145</v>
+        <v>2.015158417017853</v>
       </c>
       <c r="N4" t="n">
-        <v>6.522573401317656</v>
+        <v>6.497568346266651</v>
       </c>
       <c r="O4" t="n">
-        <v>2.553932928116488</v>
+        <v>2.549032825654988</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2886477601478</v>
+        <v>203.2820259401345</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31439,7 +31563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E945"/>
+  <dimension ref="A1:E949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56953,6 +57077,114 @@
         </is>
       </c>
     </row>
+    <row r="946">
+      <c r="A946" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:12:42+00:00</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>-41.019444936565804,173.0184001032644</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>-41.01874422543579,173.01845518944805</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>-41.01809216531276,173.01877204350072</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>-41.01944503719697,173.01840414500222</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>-41.01874468788572,173.01845809952232</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>-41.01809133097636,173.01877079485976</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>-41.0194450963917,173.01840652249507</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>-41.018744336423765,173.01845588786588</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>-41.01809234409913,173.0187723110666</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>-41.01944521478104,173.01841127748077</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>-41.018744983853665,173.01845996196988</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>-41.01809186733547,173.01877159755753</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0565/nzd0565.xlsx
+++ b/data/nzd0565/nzd0565.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E949"/>
+  <dimension ref="A1:E953"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20361,6 +20361,90 @@
       <c r="E949" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>215.06</v>
+      </c>
+      <c r="C950" t="n">
+        <v>209.54</v>
+      </c>
+      <c r="D950" t="n">
+        <v>202.25</v>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>215.59</v>
+      </c>
+      <c r="C951" t="n">
+        <v>210.14</v>
+      </c>
+      <c r="D951" t="n">
+        <v>202.31</v>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>216.13</v>
+      </c>
+      <c r="C952" t="n">
+        <v>210.26</v>
+      </c>
+      <c r="D952" t="n">
+        <v>201.96</v>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>216.58</v>
+      </c>
+      <c r="C953" t="n">
+        <v>210.32</v>
+      </c>
+      <c r="D953" t="n">
+        <v>201.13</v>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20375,7 +20459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1082"/>
+  <dimension ref="A1:B1086"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31198,6 +31282,46 @@
       </c>
       <c r="B1082" t="n">
         <v>1.81</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -31360,28 +31484,28 @@
         <v>0.1302</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03180456687789753</v>
+        <v>-0.03099337466978892</v>
       </c>
       <c r="J2" t="n">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="K2" t="n">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006970302146251273</v>
+        <v>0.006680924623007845</v>
       </c>
       <c r="M2" t="n">
-        <v>2.439518876669255</v>
+        <v>2.433566396803538</v>
       </c>
       <c r="N2" t="n">
-        <v>8.380078957563637</v>
+        <v>8.350179958360179</v>
       </c>
       <c r="O2" t="n">
-        <v>2.894836602912786</v>
+        <v>2.889667793771488</v>
       </c>
       <c r="P2" t="n">
-        <v>215.7192804642099</v>
+        <v>215.7108954318181</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31432,28 +31556,28 @@
         <v>0.0954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05232175853179667</v>
+        <v>-0.05159995780979643</v>
       </c>
       <c r="J3" t="n">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="K3" t="n">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01989624544610125</v>
+        <v>0.01953614505854551</v>
       </c>
       <c r="M3" t="n">
-        <v>2.278152104545871</v>
+        <v>2.272464632406413</v>
       </c>
       <c r="N3" t="n">
-        <v>7.867214187611925</v>
+        <v>7.837725065405587</v>
       </c>
       <c r="O3" t="n">
-        <v>2.804855466438855</v>
+        <v>2.799593732205726</v>
       </c>
       <c r="P3" t="n">
-        <v>210.6018898787566</v>
+        <v>210.5944484624766</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31504,28 +31628,28 @@
         <v>0.1109</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07211644860455413</v>
+        <v>-0.07164437978750099</v>
       </c>
       <c r="J4" t="n">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="K4" t="n">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04461212583225826</v>
+        <v>0.04444705323755738</v>
       </c>
       <c r="M4" t="n">
-        <v>2.015158417017853</v>
+        <v>2.009531207706412</v>
       </c>
       <c r="N4" t="n">
-        <v>6.497568346266651</v>
+        <v>6.472538659158891</v>
       </c>
       <c r="O4" t="n">
-        <v>2.549032825654988</v>
+        <v>2.544118444404444</v>
       </c>
       <c r="P4" t="n">
-        <v>203.2820259401345</v>
+        <v>203.2771626669214</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31563,7 +31687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E949"/>
+  <dimension ref="A1:E953"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57185,6 +57309,114 @@
         </is>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>-41.01944545747856,173.01842102520155</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>-41.018745686777365,173.0184643852829</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>-41.01809276126733,173.01877293538712</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>-41.01944561434359,173.01842732555767</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>-41.018746796656565,173.0184713694615</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>-41.01809311884008,173.01877347051897</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>-41.01944577416798,173.01843374478847</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>-41.01874701863236,173.01847276629726</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>-41.01809103299906,173.0187703489166</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>-41.01944590735471,173.0184390941475</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>-41.018747129620245,173.01847346471513</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>-41.01808608657576,173.01876294626035</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
